--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/vuse-it.xlsx
+++ b/output/vuse-it.xlsx
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
